--- a/output/pdf_financials_xlsx/ACM.xlsx
+++ b/output/pdf_financials_xlsx/ACM.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/ACM.xlsx
+++ b/output/pdf_financials_xlsx/ACM.xlsx
@@ -429,12 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,6 +462,16 @@
           <t>2023-11</t>
         </is>
       </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -480,6 +492,12 @@
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -493,6 +511,12 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -506,6 +530,12 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -519,6 +549,12 @@
       <c r="C7" s="3" t="n">
         <v>0.180883</v>
       </c>
+      <c r="D7" s="3" t="n">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2.158936</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -532,6 +568,12 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -545,6 +587,12 @@
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -558,6 +606,12 @@
       <c r="C10" s="3" t="n">
         <v>0.232253</v>
       </c>
+      <c r="D10" s="3" t="n">
+        <v>1.011022</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>4.889535</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -571,6 +625,12 @@
       <c r="C11" s="3" t="n">
         <v>-0.232253</v>
       </c>
+      <c r="D11" s="3" t="n">
+        <v>-1.011022</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-4.889535</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -584,6 +644,12 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -592,10 +658,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -610,6 +682,12 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -623,6 +701,12 @@
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -636,6 +720,12 @@
       <c r="C16" s="3" t="n">
         <v>-0.18837</v>
       </c>
+      <c r="D16" s="3" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-5.564596</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -644,10 +734,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -666,6 +762,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -683,6 +789,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -696,6 +812,12 @@
       <c r="C20" s="3" t="n">
         <v>-0.18837</v>
       </c>
+      <c r="D20" s="3" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-5.564596</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -709,6 +831,12 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -722,6 +850,12 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -735,6 +869,12 @@
       <c r="C23" s="3" t="n">
         <v>-0.18837</v>
       </c>
+      <c r="D23" s="3" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-5.564596</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -752,6 +892,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.23</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -769,6 +915,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.23</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -786,6 +938,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D26" s="3" t="n">
+        <v>1.230301</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>24.193896</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -799,6 +957,12 @@
       <c r="C27" s="3" t="n">
         <v>-0.18837</v>
       </c>
+      <c r="D27" s="3" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-5.564596</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -812,6 +976,12 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -825,6 +995,12 @@
       <c r="C29" s="3" t="n">
         <v>-0.18837</v>
       </c>
+      <c r="D29" s="3" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-5.564596</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -842,6 +1018,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -855,6 +1041,12 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -872,6 +1064,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -892,6 +1094,12 @@
       <c r="C34" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -905,6 +1113,12 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -918,6 +1132,12 @@
       <c r="C36" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -931,6 +1151,12 @@
       <c r="C37" s="3" t="n">
         <v>0.022251</v>
       </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -944,6 +1170,12 @@
       <c r="C38" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -957,6 +1189,12 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -970,6 +1208,12 @@
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -983,6 +1227,12 @@
       <c r="C41" s="3" t="n">
         <v>0.022251</v>
       </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -996,6 +1246,12 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1009,6 +1265,12 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1022,6 +1284,12 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1035,6 +1303,12 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1048,6 +1322,12 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1061,6 +1341,12 @@
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1074,6 +1360,12 @@
       <c r="C48" s="3" t="n">
         <v>0.015637</v>
       </c>
+      <c r="D48" s="3" t="n">
+        <v>0.457066</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1.579924</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1087,6 +1379,12 @@
       <c r="C49" s="3" t="n">
         <v>0.037888</v>
       </c>
+      <c r="D49" s="3" t="n">
+        <v>0.457066</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>1.579924</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1100,6 +1398,12 @@
       <c r="C50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1113,6 +1417,12 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1126,6 +1436,12 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1139,6 +1455,12 @@
       <c r="C53" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1152,6 +1474,12 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1169,6 +1497,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1182,6 +1520,12 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1195,6 +1539,12 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1208,6 +1558,12 @@
       <c r="C58" s="3" t="n">
         <v>0.366</v>
       </c>
+      <c r="D58" s="3" t="n">
+        <v>10.368428</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>10.801471</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1221,6 +1577,12 @@
       <c r="C59" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1234,6 +1596,12 @@
       <c r="C60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1247,6 +1615,12 @@
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D61" s="3" t="n">
+        <v>0.175908</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.19236</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1260,6 +1634,12 @@
       <c r="C62" s="3" t="n">
         <v>0.366</v>
       </c>
+      <c r="D62" s="3" t="n">
+        <v>10.544336</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>10.993831</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1273,6 +1653,12 @@
       <c r="C63" s="3" t="n">
         <v>0.403888</v>
       </c>
+      <c r="D63" s="3" t="n">
+        <v>11.001402</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>12.573755</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1286,6 +1672,12 @@
       <c r="C64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1299,6 +1691,12 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1312,6 +1710,12 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1325,6 +1729,12 @@
       <c r="C67" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1338,6 +1748,12 @@
       <c r="C68" s="3" t="n">
         <v>0.374681</v>
       </c>
+      <c r="D68" s="3" t="n">
+        <v>1.178526</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.898279</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1351,6 +1767,12 @@
       <c r="C69" s="3" t="n">
         <v>0.00865</v>
       </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1364,6 +1786,12 @@
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1377,6 +1805,12 @@
       <c r="C71" s="3" t="n">
         <v>0.00865</v>
       </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1390,6 +1824,12 @@
       <c r="C72" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1403,6 +1843,12 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1416,6 +1862,12 @@
       <c r="C74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1429,6 +1881,12 @@
       <c r="C75" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D75" s="3" t="n">
+        <v>4.781626</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1.756154</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1446,6 +1904,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D76" s="3" t="n">
+        <v>5.960152</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>2.654433</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1459,6 +1923,12 @@
       <c r="C77" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1472,6 +1942,12 @@
       <c r="C78" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1485,6 +1961,12 @@
       <c r="C79" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1498,6 +1980,16 @@
       <c r="C80" s="3" t="n">
         <v>0.4207812423991827</v>
       </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1511,6 +2003,12 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1524,6 +2022,12 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1537,6 +2041,12 @@
       <c r="C83" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1550,6 +2060,12 @@
       <c r="C84" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1563,6 +2079,12 @@
       <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D85" s="3" t="n">
+        <v>3.400368</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>1.75954</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -1580,6 +2102,12 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D86" s="3" t="n">
+        <v>3.400368</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>1.75954</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1593,6 +2121,12 @@
       <c r="C87" s="3" t="n">
         <v>0.383331</v>
       </c>
+      <c r="D87" s="3" t="n">
+        <v>9.360519999999999</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>4.413973</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -1606,6 +2140,12 @@
       <c r="C88" s="3" t="n">
         <v>4.258805</v>
       </c>
+      <c r="D88" s="3" t="n">
+        <v>2.128659</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>13.454179</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -1619,6 +2159,12 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -1632,6 +2178,12 @@
       <c r="C90" s="3" t="n">
         <v>-4.953629</v>
       </c>
+      <c r="D90" s="3" t="n">
+        <v>-1.266494</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-6.83109</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -1645,6 +2197,12 @@
       <c r="C91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -1658,6 +2216,12 @@
       <c r="C92" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -1671,6 +2235,12 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -1684,6 +2254,12 @@
       <c r="C94" s="3" t="n">
         <v>0.020557</v>
       </c>
+      <c r="D94" s="3" t="n">
+        <v>1.640882</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>8.159782</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -1697,6 +2273,12 @@
       <c r="C95" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -1710,6 +2292,12 @@
       <c r="C96" s="3" t="n">
         <v>0.020557</v>
       </c>
+      <c r="D96" s="3" t="n">
+        <v>1.640882</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>8.159782</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -1723,6 +2311,12 @@
       <c r="C97" s="3" t="n">
         <v>0.05089777364021709</v>
       </c>
+      <c r="D97" s="3" t="n">
+        <v>0.1491520807984291</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.648953474916602</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1743,6 +2337,12 @@
       <c r="C99" s="3" t="n">
         <v>-0.18837</v>
       </c>
+      <c r="D99" s="3" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-5.564596</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -1756,6 +2356,12 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1769,6 +2375,12 @@
       <c r="C101" s="3" t="n">
         <v>0.028193</v>
       </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -1782,6 +2394,12 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -1795,6 +2413,12 @@
       <c r="C103" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.051175</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.718218</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -1808,6 +2432,12 @@
       <c r="C104" s="3" t="n">
         <v>0.05524</v>
       </c>
+      <c r="D104" s="3" t="n">
+        <v>0.364693</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.316472</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -1821,6 +2451,12 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -1834,6 +2470,12 @@
       <c r="C106" s="3" t="n">
         <v>0.08343299999999999</v>
       </c>
+      <c r="D106" s="3" t="n">
+        <v>0.313518</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-1.03469</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -1847,6 +2489,12 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D107" s="3" t="n">
+        <v>0.377998</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>1.014139</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -1860,6 +2508,12 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -1873,6 +2527,12 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -1886,6 +2546,12 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -1899,6 +2565,12 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -1912,6 +2584,12 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -1925,6 +2603,12 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -1938,6 +2622,12 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -1951,6 +2641,12 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -1964,6 +2660,12 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -1977,6 +2679,12 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -1990,6 +2698,12 @@
       <c r="C118" s="3" t="n">
         <v>-0.035</v>
       </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.031043</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -2003,6 +2717,16 @@
       <c r="C119" s="3" t="n">
         <v>-0.055</v>
       </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -2016,6 +2740,12 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2029,6 +2759,12 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2042,6 +2778,12 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2055,6 +2797,12 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2068,6 +2816,12 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2081,6 +2835,12 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -2094,6 +2854,12 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2111,6 +2877,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2124,6 +2900,12 @@
       <c r="C128" s="3" t="n">
         <v>-0.024</v>
       </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -2137,6 +2919,12 @@
       <c r="C129" s="3" t="n">
         <v>0.0585</v>
       </c>
+      <c r="D129" s="3" t="n">
+        <v>1.518936</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>4.955348</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -2150,6 +2938,12 @@
       <c r="C130" s="3" t="n">
         <v>0.09707399999999999</v>
       </c>
+      <c r="D130" s="3" t="n">
+        <v>0.281158</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.192802</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -2163,6 +2957,12 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D131" s="3" t="n">
+        <v>-0.002653</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>-0.016812</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -2176,6 +2976,12 @@
       <c r="C132" s="3" t="n">
         <v>-0.081437</v>
       </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.088356</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.178064</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -2189,6 +2995,12 @@
       <c r="C133" s="3" t="n">
         <v>0.015637</v>
       </c>
+      <c r="D133" s="3" t="n">
+        <v>0.192802</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.370866</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -2202,6 +3014,12 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -2214,6 +3032,16 @@
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.084937</v>
+      </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E135" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2227,7 +3055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2267,6 +3095,16 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2274,26 +3112,28 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>0.09707399999999999</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0.015637</v>
+          <t>As at June 30, 2025 June</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>3e-05</v>
       </c>
     </row>
     <row r="3">
@@ -2304,24 +3144,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AccountsReceivable</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.050444</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0.022251</v>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.192802</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.370866</v>
       </c>
     </row>
     <row r="4">
@@ -2332,24 +3182,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Total Current Assets</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CurrentAssets</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.147518</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.037888</v>
+          <t>GST and VAT receivable</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.209089</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.25792</v>
       </c>
     </row>
     <row r="5">
@@ -2360,24 +3216,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets (Note 3)</t>
+          <t>Prepaid expenses (Note 6)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0.366</v>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.055175</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.733065</v>
       </c>
     </row>
     <row r="6">
@@ -2388,24 +3254,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0.478518</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0.403888</v>
+          <t>Advances (Note 17)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.218073</v>
       </c>
     </row>
     <row r="7">
@@ -2416,24 +3290,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Note 8)</t>
+          <t>Total current assets</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.319441</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.374681</v>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.457066</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.579924</v>
       </c>
     </row>
     <row r="8">
@@ -2444,24 +3328,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Loan payable (Note 4)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CurrentDebt</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0.00865</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.00865</v>
+          <t>Cash held on deposit (Note 7)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.175908</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.19236</v>
       </c>
     </row>
     <row r="9">
@@ -2472,24 +3362,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Total Liabilities</t>
+          <t>Exploration and evaluation assets (Note 8)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.328091</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.383331</v>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>10.368428</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>10.801471</v>
       </c>
     </row>
     <row r="10">
@@ -2500,24 +3400,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Share capital (Note 5)</t>
+          <t>Total assets $</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>3.855455</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>4.258805</v>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>11.001402</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>12.573755</v>
       </c>
     </row>
     <row r="11">
@@ -2528,20 +3438,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Accounts payable and accrued liabilities (Notes 9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Share-based payment reserve (Note 5)</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
-        <v>0.532231</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.715381</v>
+          <t>Accounts payable and accrued liabilities (Notes 9 and 17) $</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.178526</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.898279</v>
       </c>
     </row>
     <row r="12">
@@ -2552,22 +3476,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Accounts payable and accrued liabilities (Notes 9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Share subscriptions received (Note 5)</t>
+          <t>Accrued interest (Notes 10)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" s="5" t="n">
-        <v>0.528</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.113779</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.184557</v>
       </c>
     </row>
     <row r="13">
@@ -2578,24 +3510,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Accounts payable and accrued liabilities (Notes 9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>-4.765259</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>-4.953629</v>
+          <t>Promissory notes (Note 10)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.136597</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.231597</v>
       </c>
     </row>
     <row r="14">
@@ -2606,24 +3544,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Accounts payable and accrued liabilities (Notes 9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total Shareholders’ Equity</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.150427</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.020557</v>
+          <t>Convertible debentures (Note 11)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>3.53125</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2634,73 +3580,89 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shareholders’ Equity</t>
+          <t>Accounts payable and accrued liabilities (Notes 9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders’ Equity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0.478518</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.403888</v>
+          <t>Special warrant liability (Note 12)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.725368</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Accounts payable and accrued liabilities (Notes 9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Total current liabilities</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>-2.176811</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>-0.18837</v>
+          <t>CurrentLiabilities</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5.960152</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2.654433</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adjustment for non-cash items</t>
+          <t>Accounts payable and accrued liabilities (Notes 9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Write off of accounts payable</t>
+          <t>Total liabilities</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>TotalLiabilities</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2708,227 +3670,307 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>-0.043883</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>9.360519999999999</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>4.413973</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Adjustment for non-cash items</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets</t>
+          <t>Share capital (Note 13)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0.02</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.128659</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>13.454179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital components</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>-0.018951</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>0.028193</v>
+          <t>Share subscriptions (Note 13)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital components</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0.082292</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>0.099123</v>
+          <t>Reserves (Notes 14 and 15)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.388594</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1.621788</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital components</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>-0.48847</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>-0.084937</v>
+          <t>Other accumulated comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>-0.002377</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-0.085095</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Exploration and evaluation asset costs</t>
+          <t>Accumulated deficit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>-0.055</v>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.266494</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-6.83109</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Total shareholder’s equity</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>-0.055</v>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.640882</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>8.159782</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares</t>
+          <t>Total liabilities and shareholder’s equity $</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0.125675</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0.0825</v>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>11.001402</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>12.573755</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Share subscriptions received</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="F25" t="inlineStr">
+        <v>0.09707399999999999</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.015637</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2937,457 +3979,615 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Amounts receivable</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.050444</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.022251</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Total Current Assets</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.653675</v>
+        <v>0.147518</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.0585</v>
+        <v>0.037888</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Change in cash</t>
+          <t>Exploration and evaluation assets (Note 3)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.085205</v>
+        <v>0.331</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.081437</v>
+        <v>0.366</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.011869</v>
+        <v>0.478518</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.09707399999999999</v>
+        <v>0.403888</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cash, end of the year</t>
+          <t>Accounts payable and accrued liabilities (Note 8)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.09707399999999999</v>
+        <v>0.319441</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.015637</v>
+        <v>0.374681</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 8)</t>
+          <t>Loan payable (Note 4)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.302121</v>
+        <v>0.00865</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.120049</v>
+        <v>0.00865</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 3)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
-        <v>0.142137</v>
+        <v>0.328091</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.009594</v>
+        <v>0.383331</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 3)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Share capital (Note 5)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
-        <v>1.625</v>
+        <v>3.855455</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.02</v>
+        <v>4.258805</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based payment reserve (Note 5)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.034685</v>
+        <v>0.532231</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0305</v>
+        <v>0.715381</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share subscriptions received (Note 5)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
-        <v>0.002383</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>0.001399</v>
+        <v>0.528</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.015153</v>
+        <v>-4.765259</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.021776</v>
+        <v>-4.953629</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rent (Note 8)</t>
+          <t>Total Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.012</v>
+        <v>0.150427</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.012</v>
+        <v>0.020557</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Total Liabilities and Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.018066</v>
+        <v>0.478518</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.016935</v>
+        <v>0.403888</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Loss for the year $</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0.025266</v>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>-5.564596</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Total administrative and operating expenses</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>2.176811</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.232253</v>
+          <t>(Gain) loss on revaluation of special warrant liability</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.020531</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>-0.385368</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net loss before other item</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" s="5" t="n">
-        <v>-2.176811</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>-0.232253</v>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.377998</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1.014139</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Write off of accounts payable</t>
+          <t>Shares issued for services</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -3396,265 +4596,377 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>0.043883</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>-2.176811</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>-0.18837</v>
+          <t>Capital contribution from a shareholder</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.4275</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per common share</t>
+          <t>Accrued interest</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.113779</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0.558419</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>76.93651199999999</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>87.66797699999999</v>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.508893</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2021 74,845,580 3,729,780 532,231 –</t>
+          <t>GST and VAT receivable</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" s="5" t="n">
-        <v>1.673563</v>
-      </c>
-      <c r="F46" s="5" t="n">
-        <v>-2.588448</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>-0.09289600000000001</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>-0.035653</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Flow-through units issued for cash 2,285,000 125,675 – –</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>0.125675</v>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.051175</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>-0.718218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Share subscriptions received – – – 528,000</t>
+          <t>Advances</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>0.528</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>-0.218073</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Net loss for the year – – – –</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>-2.176811</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-2.176811</v>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.364693</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>-0.316472</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Balance, November 30, 2022 77,130,580 3,855,455 532,231 528,000</t>
+          <t>Net cash used in operations</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>0.150427</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>-4.765259</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.38135</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>-4.729429</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Units issued for cash 12,210,000 427,350 183,150 (528,000)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>0.0825</v>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>-0.031043</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Finder’s fees paid in cash – (24,000) – –</t>
+          <t>Acquisition of PanMetals</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>-0.024</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-1.341451</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3663,25 +4975,3087 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cash received on acquisition</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.118162</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Net cash to investing activities</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-1.223289</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>-0.031043</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Common shares subscribed and issued, net of issue costs</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>1.101436</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>4.745748</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Proceeds from the finders’ warrants exercised</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>0.0159</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Proceeds from the subscription warrants exercised</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Repayment of promissory notes</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>-0.2938</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Common shares issued for options exercised</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Subscriptions received</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Net cash provided from financing activities</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>1.518936</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>4.955348</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Effects of foreign exchange on cash</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.002653</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>-0.016812</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.088356</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.178064</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.281158</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0.192802</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.192802</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.370866</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1. NATURE OF OPERATIONS AND CONTINUANCE OF BUSINESS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Columbia Business Corporations Act. On November 14, 2018, Deeprock completed its initial public offering and commenced trading on the Canadian Securities Exchange on November</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>1.6e-05</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>on tungsten projects in Portugal.</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Pursuant to an acquisition agreement dated February 15, 2023, and amended on June</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>on tungsten projects in Portugal.</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>wholly owned subsidiary of a company (the “Resulting Issuer”) whose common shares (the “RI Shares”) would be listed and posted for trading on a Canadian stock exchange on or before June</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>on tungsten projects in Portugal.</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>(subsequently amended to April 30, 2025). On April 29, 2024, the Company completed the Acquisition of all issued and outstanding shares of PanMetals. The Listing was completed on April</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>1.7e-05</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Basis of presentation</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>The consolidated financial statements were approved by the Board of Directors as of October</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>2.8e-05</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>-2.176811</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.18837</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Adjustment for non-cash items</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Write off of accounts payable</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-0.043883</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Adjustment for non-cash items</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital components</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>-0.018951</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.028193</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital components</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0.082292</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.099123</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital components</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>-0.48847</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>-0.084937</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation asset costs</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of shares</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.125675</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Share subscriptions received</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0.653675</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Change in cash</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0.085205</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>-0.081437</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0.011869</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0.09707399999999999</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Cash, end of the year</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0.09707399999999999</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0.015637</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Shares Amount reserve Receivable Deficit Equity</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Consulting fees $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>1.340943</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.356531</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>1.197868</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 17)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.377998</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>1.014139</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.088837</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0.402778</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Management fees (Note 17)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0.261272</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>0.119028</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.03385</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.115814</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0.083693</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.041111</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Project investigation costs</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.027195</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>1.011022</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>4.889535</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Financing costs and miscellaneous income (loss)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Listing expense (Note 4)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>-0.508893</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Financing costs and miscellaneous income (loss)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Interest expense (Note 10 and 11)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>InterestExpense</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-0.113779</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>-0.561642</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Gain (loss) on revaluation of special warrant</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Gain (loss) on revaluation of special warrant liability (Note 12)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-0.020531</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>0.385368</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Gain (loss) on revaluation of special warrant</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0.010106</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gain (loss) on revaluation of special warrant</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-1.14418</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>-5.564596</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Translation expense</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>-0.002377</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>-0.082718</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>-1.146557</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>-5.647314</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Weighted average shares outstanding – basic and</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>1.234778</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>24.186536</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>diluted</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>-9.300000000000001e-07</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>-2.3e-07</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>diluted</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>diluted total</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>| Equity 857,113 1,134,850 (130,022) 30,000 25,000 492,500 377,988 (1,146,557) 1,640,882 699,650 175,460 427,500 485,000 508,893 4,653,131 (723,310) 4,907,351 15,900 2,500 1,014,139</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>8.159782</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>-5.647314</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>$        $                 $                                                                                                                    Shareholders’</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>$        $                 $                                                                                                                    Shareholders’</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Accumulated Deficit              (122,314)$                                                                                (1,144,180) (1,266,494)$                                                                                                                                                                            (5,564,596) (6,831,090)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Accumulated Deficit              (122,314)$                                                                                (1,144,180) (1,266,494)$                                                                                                                                                                            (5,564,596) (6,831,090)$</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Accumulated Deficit              (122,314)$                                                                                (1,144,180) (1,266,494)$                                                                                                                                                                            (5,564,596) (6,831,090)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Other (2,377) (2,377)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-0.085095</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>-0.082718</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>$        $                 $                                                                                                                    Comprehensive                                                                                     Accumulated</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Reserves 27,360 2,296 (19,060) 377,998 388,594 427,500 (377,998) 1,928 142,775 33,150 (8,300)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>1.621788</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>1.014139</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>$                 $                                                      Capital                      Equity                                                                                                                                                                                                                              notes</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>$                 $                                                      Capital                      Equity                                                                                                                                                                                                                              notes</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0.302121</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0.120049</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Exploration expenditures (Note 3)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>0.142137</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.009594</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets (Note 3)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0.034685</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Office and miscellaneous</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.002383</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.001399</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.015153</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.021776</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Rent (Note 8)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.018066</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.016935</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>0.025266</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Total administrative and operating expenses</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>2.176811</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.232253</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Net loss before other item</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>-2.176811</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>-0.232253</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Write off of accounts payable</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0.043883</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>-2.176811</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>-0.18837</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Basic and diluted net loss per common share</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Other item</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>76.93651199999999</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>87.66797699999999</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Balance, November 30, 2021 74,845,580 3,729,780 532,231 –</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="n">
+        <v>1.673563</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>-2.588448</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Flow-through units issued for cash 2,285,000 125,675 – –</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" s="5" t="n">
+        <v>0.125675</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Share subscriptions received – – – 528,000</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Net loss for the year – – – –</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>-2.176811</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>-2.176811</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Balance, November 30, 2022 77,130,580 3,855,455 532,231 528,000</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" s="5" t="n">
+        <v>0.150427</v>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>-4.765259</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Units issued for cash 12,210,000 427,350 183,150 (528,000)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" s="5" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Finder’s fees paid in cash – (24,000) – –</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Shares      Amount       reserve     Receivable        Deficit         Equity</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>Balance, November 30, 2023 89,340,580 4,258,805 715,381 –</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" s="5" t="n">
         <v>0.020557</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F136" s="5" t="n">
         <v>-4.953629</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/ACM.xlsx
+++ b/output/pdf_financials_xlsx/ACM.xlsx
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.532231</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.715381</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.388594</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.621788</v>
       </c>
     </row>
     <row r="93">
@@ -3772,7 +3772,11 @@
           <t>Reserves (Notes 14 and 15)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -4296,7 +4300,11 @@
           <t>Share-based payment reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.532231</v>
       </c>

--- a/output/pdf_financials_xlsx/ACM.xlsx
+++ b/output/pdf_financials_xlsx/ACM.xlsx
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001152</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.010106</v>
       </c>
     </row>
     <row r="13">
@@ -958,10 +958,10 @@
         <v>-0.18837</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.14418</v>
+        <v>-1.145332</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.564596</v>
+        <v>-5.574702</v>
       </c>
     </row>
     <row r="28">
@@ -996,10 +996,10 @@
         <v>-0.18837</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.14418</v>
+        <v>-1.145332</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.564596</v>
+        <v>-5.574702</v>
       </c>
     </row>
     <row r="30">
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.09707399999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.015637</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.192802</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.370866</v>
       </c>
     </row>
     <row r="35">
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.09707399999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.015637</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.192802</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.370866</v>
       </c>
     </row>
     <row r="37">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.09707399999999999</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.015637</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.457066</v>
+        <v>0.264264</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.579924</v>
+        <v>1.209058</v>
       </c>
     </row>
     <row r="49">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">

--- a/output/pdf_financials_xlsx/ACM.xlsx
+++ b/output/pdf_financials_xlsx/ACM.xlsx
@@ -1730,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.126607</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.049842</v>
       </c>
     </row>
     <row r="68">
